--- a/submissions/11-lien-analysis-larkspur/inputs/owner_project_file_larkspur.xlsx
+++ b/submissions/11-lien-analysis-larkspur/inputs/owner_project_file_larkspur.xlsx
@@ -3,15 +3,16 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA19907-74B7-8D4A-8EDE-D42F65615547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8C10F3-AC3A-E44D-8FCF-FD61E39C389F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="21600" windowHeight="36520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Prelim Log" sheetId="1" r:id="rId1"/>
     <sheet name="Waiver Log" sheetId="2" r:id="rId2"/>
     <sheet name="Owner Payments" sheetId="3" r:id="rId3"/>
     <sheet name="Subcontractors" sheetId="4" r:id="rId4"/>
+    <sheet name="Certified Mail" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="291">
   <si>
     <t>Preliminary notices received, Larkspur Crossing Building B, job file 2210-B</t>
   </si>
@@ -63,9 +64,6 @@
     <t>ESTIMATED_VALUE</t>
   </si>
   <si>
-    <t>SERVED_ON</t>
-  </si>
-  <si>
     <t>Ostrowski Electric, Inc.</t>
   </si>
   <si>
@@ -87,9 +85,6 @@
     <t>01/19/2026</t>
   </si>
   <si>
-    <t>Owner and direct contractor</t>
-  </si>
-  <si>
     <t>Tallac Concrete, Inc.</t>
   </si>
   <si>
@@ -108,21 +103,48 @@
     <t>02/02/2026</t>
   </si>
   <si>
+    <t>Foothill Ready Mix, Inc.</t>
+  </si>
+  <si>
+    <t>Ready mixed concrete</t>
+  </si>
+  <si>
+    <t>02/10/2026</t>
+  </si>
+  <si>
+    <t>02/13/2026</t>
+  </si>
+  <si>
+    <t>02/05/2026</t>
+  </si>
+  <si>
     <t>Petrakis Plumbing, Inc.</t>
   </si>
   <si>
     <t>Plumbing</t>
   </si>
   <si>
-    <t>02/10/2026</t>
-  </si>
-  <si>
     <t>02/12/2026</t>
   </si>
   <si>
     <t>02/17/2026</t>
   </si>
   <si>
+    <t>Capitol Wire &amp; Lighting, Inc.</t>
+  </si>
+  <si>
+    <t>Switchgear, wire, fixtures</t>
+  </si>
+  <si>
+    <t>02/16/2026</t>
+  </si>
+  <si>
+    <t>02/18/2026</t>
+  </si>
+  <si>
+    <t>02/04/2026</t>
+  </si>
+  <si>
     <t>R. Nakamura Framing, Inc.</t>
   </si>
   <si>
@@ -156,7 +178,7 @@
     <t>03/11/2026</t>
   </si>
   <si>
-    <t>Fenwick Roofing Systems</t>
+    <t>Fenwick Roofing, Inc.</t>
   </si>
   <si>
     <t>Roofing</t>
@@ -168,15 +190,27 @@
     <t>03/16/2026</t>
   </si>
   <si>
+    <t>Sierra Pipe &amp; Supply, Inc.</t>
+  </si>
+  <si>
+    <t>Pipe, fittings, fixtures</t>
+  </si>
+  <si>
+    <t>03/13/2026</t>
+  </si>
+  <si>
+    <t>03/18/2026</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
     <t>Kastner Mechanical Contractors, Inc.</t>
   </si>
   <si>
     <t>HVAC</t>
   </si>
   <si>
-    <t>03/18/2026</t>
-  </si>
-  <si>
     <t>03/20/2026</t>
   </si>
   <si>
@@ -201,24 +235,33 @@
     <t>04/20/2026</t>
   </si>
   <si>
+    <t>Calder Bros. Masonry, Inc.</t>
+  </si>
+  <si>
+    <t>Masonry veneer, trash enclosure</t>
+  </si>
+  <si>
+    <t>04/27/2026</t>
+  </si>
+  <si>
+    <t>04/29/2026</t>
+  </si>
+  <si>
+    <t>05/01/2026</t>
+  </si>
+  <si>
     <t>Abrego Glass &amp; Glazing</t>
   </si>
   <si>
     <t>Storefront and glazing</t>
   </si>
   <si>
-    <t>05/01/2026</t>
-  </si>
-  <si>
     <t>05/04/2026</t>
   </si>
   <si>
     <t>05/06/2026</t>
   </si>
   <si>
-    <t>04/27/2026</t>
-  </si>
-  <si>
     <t>Bautista Painting Co.</t>
   </si>
   <si>
@@ -243,289 +286,334 @@
     <t>Lumber, trusses, sheathing</t>
   </si>
   <si>
-    <t>05/28/2026</t>
-  </si>
-  <si>
     <t>06/02/2026</t>
   </si>
   <si>
-    <t>04/06/2026</t>
+    <t>05/11/2026</t>
+  </si>
+  <si>
+    <t>Waivers and releases received with payment applications, Larkspur Crossing Building B</t>
+  </si>
+  <si>
+    <t>FORM_TITLE is the title printed on the document received; PAY_APP is the payment application the document came in with. CHECK_REF is the check the form names, where the form names one. EXCEPTIONS is what the form lists as excepted. The log continues in the right-hand block, columns J to R.</t>
+  </si>
+  <si>
+    <t>CLAIMANT</t>
+  </si>
+  <si>
+    <t>PAY_APP</t>
+  </si>
+  <si>
+    <t>FORM_TITLE</t>
+  </si>
+  <si>
+    <t>THROUGH_DATE</t>
+  </si>
+  <si>
+    <t>AMOUNT</t>
+  </si>
+  <si>
+    <t>EXCEPTIONS</t>
+  </si>
+  <si>
+    <t>CHECK_REF</t>
+  </si>
+  <si>
+    <t>DATE_SIGNED</t>
+  </si>
+  <si>
+    <t>CLAIMANT_2</t>
+  </si>
+  <si>
+    <t>PAY_APP_2</t>
+  </si>
+  <si>
+    <t>FORM_TITLE_2</t>
+  </si>
+  <si>
+    <t>THROUGH_DATE_2</t>
+  </si>
+  <si>
+    <t>AMOUNT_2</t>
+  </si>
+  <si>
+    <t>EXCEPTIONS_2</t>
+  </si>
+  <si>
+    <t>CHECK_REF_2</t>
+  </si>
+  <si>
+    <t>DATE_SIGNED_2</t>
+  </si>
+  <si>
+    <t>RECEIVED_2</t>
+  </si>
+  <si>
+    <t>Unconditional Waiver and Release on Progress Payment</t>
+  </si>
+  <si>
+    <t>05/31/2026</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>07/01/2026</t>
+  </si>
+  <si>
+    <t>07/06/2026</t>
+  </si>
+  <si>
+    <t>02/28/2026</t>
+  </si>
+  <si>
+    <t>03/31/2026</t>
+  </si>
+  <si>
+    <t>04/03/2026</t>
+  </si>
+  <si>
+    <t>06/30/2026</t>
+  </si>
+  <si>
+    <t>08/03/2026</t>
+  </si>
+  <si>
+    <t>05/05/2026</t>
+  </si>
+  <si>
+    <t>07/02/2026</t>
+  </si>
+  <si>
+    <t>04/30/2026</t>
+  </si>
+  <si>
+    <t>06/01/2026</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
+  </si>
+  <si>
+    <t>07/31/2026</t>
+  </si>
+  <si>
+    <t>08/26/2026</t>
+  </si>
+  <si>
+    <t>Conditional Waiver and Release on Progress Payment</t>
+  </si>
+  <si>
+    <t>Dunmore-Kettle Builders check 4461</t>
+  </si>
+  <si>
+    <t>08/19/2026</t>
+  </si>
+  <si>
+    <t>08/11/2026</t>
+  </si>
+  <si>
+    <t>Dunmore-Kettle Builders check 4479</t>
+  </si>
+  <si>
+    <t>09/30/2026</t>
+  </si>
+  <si>
+    <t>10/01/2026</t>
+  </si>
+  <si>
+    <t>Subcontractor's Release and Affidavit, Dunmore-Kettle form S-9</t>
+  </si>
+  <si>
+    <t>None stated</t>
+  </si>
+  <si>
+    <t>07/30/2026</t>
+  </si>
+  <si>
+    <t>08/24/2026</t>
+  </si>
+  <si>
+    <t>08/27/2026</t>
+  </si>
+  <si>
+    <t>Conditional Waiver and Release on Final Payment</t>
+  </si>
+  <si>
+    <t>Disputed claims for extras: $0.00</t>
+  </si>
+  <si>
+    <t>Dunmore-Kettle Builders check 4448</t>
+  </si>
+  <si>
+    <t>07/29/2026</t>
+  </si>
+  <si>
+    <t>03/30/2026</t>
+  </si>
+  <si>
+    <t>Dunmore-Kettle Builders check 4460</t>
+  </si>
+  <si>
+    <t>08/18/2026</t>
+  </si>
+  <si>
+    <t>Lien release letter on Tallac Concrete letterhead</t>
+  </si>
+  <si>
+    <t>05/08/2026</t>
+  </si>
+  <si>
+    <t>Letter says all claims for the May billing and retention are released on payment of the balance</t>
+  </si>
+  <si>
+    <t>Payments by the owner, Larkspur Crossing Building B. Dunmore-Kettle Builders, Inc., contract sum $3,748,250.00, approved change orders 1 to 6 $46,000.00, adjusted contract sum $3,794,250.00, retention 5 percent</t>
+  </si>
+  <si>
+    <t>PERIOD_THROUGH</t>
+  </si>
+  <si>
+    <t>AMOUNT_CERTIFIED</t>
+  </si>
+  <si>
+    <t>RETENTION_WITHHELD</t>
+  </si>
+  <si>
+    <t>AMOUNT_PAID</t>
+  </si>
+  <si>
+    <t>CHECK_NO</t>
+  </si>
+  <si>
+    <t>CHECK_DATE</t>
+  </si>
+  <si>
+    <t>CLEARED</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>01/31/2026</t>
+  </si>
+  <si>
+    <t>02/20/2026</t>
+  </si>
+  <si>
+    <t>02/25/2026</t>
+  </si>
+  <si>
+    <t>Paid, cleared</t>
+  </si>
+  <si>
+    <t>03/25/2026</t>
+  </si>
+  <si>
+    <t>04/21/2026</t>
+  </si>
+  <si>
+    <t>05/21/2026</t>
+  </si>
+  <si>
+    <t>06/19/2026</t>
+  </si>
+  <si>
+    <t>06/24/2026</t>
+  </si>
+  <si>
+    <t>07/22/2026</t>
+  </si>
+  <si>
+    <t>07/27/2026</t>
+  </si>
+  <si>
+    <t>08/14/2026</t>
+  </si>
+  <si>
+    <t>Held pending resolution of recorded claims</t>
+  </si>
+  <si>
+    <t>Retention release</t>
+  </si>
+  <si>
+    <t>Not paid; requested with application 8</t>
+  </si>
+  <si>
+    <t>Totals</t>
+  </si>
+  <si>
+    <t>Retention withheld to date on applications 1 through 8 is the figure the direct contractor asks to have released with application 8.</t>
+  </si>
+  <si>
+    <t>Agreements the owner signed itself for the same project, paid from the owner's account</t>
+  </si>
+  <si>
+    <t>VENDOR</t>
+  </si>
+  <si>
+    <t>SCOPE</t>
+  </si>
+  <si>
+    <t>AGREEMENT_DATE</t>
+  </si>
+  <si>
+    <t>AGREEMENT_AMOUNT</t>
+  </si>
+  <si>
+    <t>PAID_TO_DATE</t>
+  </si>
+  <si>
+    <t>LAST_PAYMENT</t>
+  </si>
+  <si>
+    <t>BALANCE</t>
+  </si>
+  <si>
+    <t>WAIVER_ON_FILE</t>
+  </si>
+  <si>
+    <t>Wexford Land Surveying</t>
+  </si>
+  <si>
+    <t>Construction staking and ALTA survey</t>
+  </si>
+  <si>
+    <t>01/08/2026</t>
+  </si>
+  <si>
+    <t>07/24/2026</t>
+  </si>
+  <si>
+    <t>None requested</t>
+  </si>
+  <si>
+    <t>Paid in full</t>
+  </si>
+  <si>
+    <t>Placer Materials Testing</t>
+  </si>
+  <si>
+    <t>Special inspection and materials testing</t>
+  </si>
+  <si>
+    <t>01/12/2026</t>
+  </si>
+  <si>
+    <t>08/21/2026</t>
   </si>
   <si>
     <t>Sorensen Landscape Co.</t>
   </si>
   <si>
-    <t>Landscape and irrigation</t>
-  </si>
-  <si>
-    <t>06/12/2026</t>
-  </si>
-  <si>
-    <t>06/15/2026</t>
-  </si>
-  <si>
-    <t>06/17/2026</t>
-  </si>
-  <si>
-    <t>06/08/2026</t>
-  </si>
-  <si>
-    <t>Capitol Door &amp; Hardware</t>
-  </si>
-  <si>
-    <t>Doors, frames, hardware</t>
-  </si>
-  <si>
-    <t>06/19/2026</t>
-  </si>
-  <si>
-    <t>06/22/2026</t>
-  </si>
-  <si>
-    <t>06/24/2026</t>
-  </si>
-  <si>
-    <t>06/16/2026</t>
-  </si>
-  <si>
-    <t>Waivers and releases received with payment applications, Larkspur Crossing Building B</t>
-  </si>
-  <si>
-    <t>FORM_TITLE is the title printed on the document received; PAY_APP is the payment application the document came in with. CHECK_REF is the check the form names, where the form names one. EXCEPTIONS is what the form lists as excepted. The log continues in the right-hand block, columns J to R.</t>
-  </si>
-  <si>
-    <t>CLAIMANT</t>
-  </si>
-  <si>
-    <t>PAY_APP</t>
-  </si>
-  <si>
-    <t>FORM_TITLE</t>
-  </si>
-  <si>
-    <t>THROUGH_DATE</t>
-  </si>
-  <si>
-    <t>AMOUNT</t>
-  </si>
-  <si>
-    <t>EXCEPTIONS</t>
-  </si>
-  <si>
-    <t>CHECK_REF</t>
-  </si>
-  <si>
-    <t>DATE_SIGNED</t>
-  </si>
-  <si>
-    <t>CLAIMANT_2</t>
-  </si>
-  <si>
-    <t>PAY_APP_2</t>
-  </si>
-  <si>
-    <t>FORM_TITLE_2</t>
-  </si>
-  <si>
-    <t>THROUGH_DATE_2</t>
-  </si>
-  <si>
-    <t>AMOUNT_2</t>
-  </si>
-  <si>
-    <t>EXCEPTIONS_2</t>
-  </si>
-  <si>
-    <t>CHECK_REF_2</t>
-  </si>
-  <si>
-    <t>DATE_SIGNED_2</t>
-  </si>
-  <si>
-    <t>RECEIVED_2</t>
-  </si>
-  <si>
-    <t>Unconditional Waiver and Release on Progress Payment</t>
-  </si>
-  <si>
-    <t>05/31/2026</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>07/01/2026</t>
-  </si>
-  <si>
-    <t>07/06/2026</t>
-  </si>
-  <si>
-    <t>02/28/2026</t>
-  </si>
-  <si>
-    <t>03/31/2026</t>
-  </si>
-  <si>
-    <t>04/03/2026</t>
-  </si>
-  <si>
-    <t>06/30/2026</t>
-  </si>
-  <si>
-    <t>08/03/2026</t>
-  </si>
-  <si>
-    <t>05/05/2026</t>
-  </si>
-  <si>
-    <t>07/02/2026</t>
-  </si>
-  <si>
-    <t>04/30/2026</t>
-  </si>
-  <si>
-    <t>06/01/2026</t>
-  </si>
-  <si>
-    <t>06/03/2026</t>
-  </si>
-  <si>
-    <t>07/31/2026</t>
-  </si>
-  <si>
-    <t>Retention: $3,845.00</t>
-  </si>
-  <si>
-    <t>08/20/2026</t>
-  </si>
-  <si>
-    <t>Conditional Waiver and Release on Progress Payment</t>
-  </si>
-  <si>
-    <t>Dunmore-Kettle Builders check 4461</t>
-  </si>
-  <si>
-    <t>08/19/2026</t>
-  </si>
-  <si>
-    <t>07/30/2026</t>
-  </si>
-  <si>
-    <t>08/24/2026</t>
-  </si>
-  <si>
-    <t>08/27/2026</t>
-  </si>
-  <si>
-    <t>Conditional Waiver and Release on Final Payment</t>
-  </si>
-  <si>
-    <t>Dunmore-Kettle Builders check 4448</t>
-  </si>
-  <si>
-    <t>07/29/2026</t>
-  </si>
-  <si>
-    <t>Unconditional Waiver and Release on Final Payment</t>
-  </si>
-  <si>
-    <t>08/07/2026</t>
-  </si>
-  <si>
-    <t>08/14/2026</t>
-  </si>
-  <si>
-    <t>03/30/2026</t>
-  </si>
-  <si>
-    <t>Dunmore-Kettle Builders check 4460</t>
-  </si>
-  <si>
-    <t>08/18/2026</t>
-  </si>
-  <si>
-    <t>Lien release letter on Tallac Concrete letterhead</t>
-  </si>
-  <si>
-    <t>05/08/2026</t>
-  </si>
-  <si>
-    <t>Letter says all claims for the May billing and retention are released on payment of the balance</t>
-  </si>
-  <si>
-    <t>Payments by the owner to Dunmore-Kettle Builders, Inc., contract sum $3,748,250.00, retention 5 percent</t>
-  </si>
-  <si>
-    <t>PERIOD_THROUGH</t>
-  </si>
-  <si>
-    <t>AMOUNT_CERTIFIED</t>
-  </si>
-  <si>
-    <t>RETENTION_WITHHELD</t>
-  </si>
-  <si>
-    <t>AMOUNT_PAID</t>
-  </si>
-  <si>
-    <t>CHECK_NO</t>
-  </si>
-  <si>
-    <t>CHECK_DATE</t>
-  </si>
-  <si>
-    <t>CLEARED</t>
-  </si>
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>01/31/2026</t>
-  </si>
-  <si>
-    <t>02/04/2026</t>
-  </si>
-  <si>
-    <t>02/20/2026</t>
-  </si>
-  <si>
-    <t>02/25/2026</t>
-  </si>
-  <si>
-    <t>Paid, cleared</t>
-  </si>
-  <si>
-    <t>03/25/2026</t>
-  </si>
-  <si>
-    <t>04/21/2026</t>
-  </si>
-  <si>
-    <t>05/21/2026</t>
-  </si>
-  <si>
-    <t>07/22/2026</t>
-  </si>
-  <si>
-    <t>07/27/2026</t>
-  </si>
-  <si>
-    <t>08/11/2026</t>
-  </si>
-  <si>
-    <t>Held pending resolution of recorded claims</t>
-  </si>
-  <si>
-    <t>Retention release</t>
-  </si>
-  <si>
-    <t>Not paid; requested with application 8</t>
-  </si>
-  <si>
-    <t>Totals</t>
-  </si>
-  <si>
-    <t>Retention withheld to date on applications 1 through 8 is the figure the direct contractor asks to have released with application 8.</t>
+    <t>Landscape planting, irrigation, site furnishings</t>
+  </si>
+  <si>
+    <t>05/19/2026</t>
+  </si>
+  <si>
+    <t>Unconditional Waiver and Release on Progress Payment through 07/31/2026, signed 08/14/2026</t>
+  </si>
+  <si>
+    <t>Final invoice held, plant replacement on the punch list</t>
   </si>
   <si>
     <t>Subcontractor list submitted by Dunmore-Kettle Builders, Inc. with payment application 1, updated through application 7</t>
@@ -555,24 +643,15 @@
     <t>12/30/2025</t>
   </si>
   <si>
-    <t>Consolidated Electrical Distributors</t>
-  </si>
-  <si>
     <t>01/06/2026</t>
   </si>
   <si>
-    <t>Norcal Rebar &amp; Mesh, LLC; Foothill Ready Mix</t>
+    <t>Norcal Rebar &amp; Mesh, LLC; Foothill Ready Mix, Inc.</t>
   </si>
   <si>
     <t>01/22/2026</t>
   </si>
   <si>
-    <t>Ferguson Enterprises</t>
-  </si>
-  <si>
-    <t>02/18/2026</t>
-  </si>
-  <si>
     <t>Norman S. Wright; Sierra Test and Balance (sub-tier)</t>
   </si>
   <si>
@@ -582,7 +661,250 @@
     <t>04/08/2026</t>
   </si>
   <si>
-    <t>05/19/2026</t>
+    <t>04/14/2026</t>
+  </si>
+  <si>
+    <t>Outgoing certified mail, job file 2210-B, Larkspur Crossing Building B</t>
+  </si>
+  <si>
+    <t>Kept by the construction manager. RETURN_RECEIPT is the date on the green card when it came back, blank where it has not.</t>
+  </si>
+  <si>
+    <t>ARTICLE_NO</t>
+  </si>
+  <si>
+    <t>ADDRESSEE</t>
+  </si>
+  <si>
+    <t>CITY</t>
+  </si>
+  <si>
+    <t>CONTENTS</t>
+  </si>
+  <si>
+    <t>RETURN_RECEIPT</t>
+  </si>
+  <si>
+    <t>03/17/2026</t>
+  </si>
+  <si>
+    <t>7021 0950 0001 8842 1176</t>
+  </si>
+  <si>
+    <t>City of Roseville, Building Division</t>
+  </si>
+  <si>
+    <t>Roseville</t>
+  </si>
+  <si>
+    <t>Revised sheet S-201 and engineer's letter, permit B25-1187</t>
+  </si>
+  <si>
+    <t>03/19/2026</t>
+  </si>
+  <si>
+    <t>05/14/2026</t>
+  </si>
+  <si>
+    <t>7021 0950 0001 8842 1244</t>
+  </si>
+  <si>
+    <t>Dunmore-Kettle Builders</t>
+  </si>
+  <si>
+    <t>Rocklin</t>
+  </si>
+  <si>
+    <t>Owner's decision on change order request 6</t>
+  </si>
+  <si>
+    <t>05/15/2026</t>
+  </si>
+  <si>
+    <t>7021 0950 0001 8842 1329</t>
+  </si>
+  <si>
+    <t>Tallac Concrete Inc</t>
+  </si>
+  <si>
+    <t>Lincoln</t>
+  </si>
+  <si>
+    <t>Letter on claim of lien, Doc. No. 2026-0060418</t>
+  </si>
+  <si>
+    <t>07/09/2026</t>
+  </si>
+  <si>
+    <t>7021 0950 0001 8842 1367</t>
+  </si>
+  <si>
+    <t>Foothill Ready Mix</t>
+  </si>
+  <si>
+    <t>Loomis</t>
+  </si>
+  <si>
+    <t>Letter on claim of lien, Doc. No. 2026-0063905</t>
+  </si>
+  <si>
+    <t>07/13/2026</t>
+  </si>
+  <si>
+    <t>08/31/2026</t>
+  </si>
+  <si>
+    <t>7022 1670 0002 3391 4108</t>
+  </si>
+  <si>
+    <t>Ostrowski Electric Inc</t>
+  </si>
+  <si>
+    <t>Sacramento</t>
+  </si>
+  <si>
+    <t>Copy of notice of completion, Doc. No. 2026-0081562</t>
+  </si>
+  <si>
+    <t>09/02/2026</t>
+  </si>
+  <si>
+    <t>7022 1670 0002 3391 4122</t>
+  </si>
+  <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>7022 1670 0002 3391 4153</t>
+  </si>
+  <si>
+    <t>R Nakamura Framing</t>
+  </si>
+  <si>
+    <t>Newcastle</t>
+  </si>
+  <si>
+    <t>7022 1670 0002 3391 4160</t>
+  </si>
+  <si>
+    <t>Rancho Cordova</t>
+  </si>
+  <si>
+    <t>7022 1670 0002 3391 4191</t>
+  </si>
+  <si>
+    <t>Fenwick Roofing Inc</t>
+  </si>
+  <si>
+    <t>09/01/2026</t>
+  </si>
+  <si>
+    <t>7022 1670 0002 3391 4214</t>
+  </si>
+  <si>
+    <t>Kastner Mechanical</t>
+  </si>
+  <si>
+    <t>7022 1670 0002 3391 4238</t>
+  </si>
+  <si>
+    <t>Abrego Glass and Glazing</t>
+  </si>
+  <si>
+    <t>09/04/2026</t>
+  </si>
+  <si>
+    <t>7022 1670 0002 3391 4252</t>
+  </si>
+  <si>
+    <t>Calder Bros Masonry</t>
+  </si>
+  <si>
+    <t>Penryn</t>
+  </si>
+  <si>
+    <t>7022 1670 0002 3391 4283</t>
+  </si>
+  <si>
+    <t>09/08/2026</t>
+  </si>
+  <si>
+    <t>7022 1670 0002 3391 4337</t>
+  </si>
+  <si>
+    <t>Petrakis Plumbing</t>
+  </si>
+  <si>
+    <t>09/09/2026</t>
+  </si>
+  <si>
+    <t>7022 1670 0002 3391 4351</t>
+  </si>
+  <si>
+    <t>Bautista Painting</t>
+  </si>
+  <si>
+    <t>09/10/2026</t>
+  </si>
+  <si>
+    <t>7022 1670 0002 3391 4375</t>
+  </si>
+  <si>
+    <t>Hedrick and Sons Bldg Supply</t>
+  </si>
+  <si>
+    <t>Auburn</t>
+  </si>
+  <si>
+    <t>09/11/2026</t>
+  </si>
+  <si>
+    <t>7022 1670 0002 3391 4399</t>
+  </si>
+  <si>
+    <t>Sierra Pipe and Supply</t>
+  </si>
+  <si>
+    <t>7022 1670 0002 3391 4629</t>
+  </si>
+  <si>
+    <t>7022 1670 0002 3391 4643</t>
+  </si>
+  <si>
+    <t>Capitol Wire and Lighting</t>
+  </si>
+  <si>
+    <t>09/14/2026</t>
+  </si>
+  <si>
+    <t>09/22/2026</t>
+  </si>
+  <si>
+    <t>7022 1670 0002 3391 4711</t>
+  </si>
+  <si>
+    <t>Notice that payment application 8 is held</t>
+  </si>
+  <si>
+    <t>09/23/2026</t>
+  </si>
+  <si>
+    <t>09/24/2026</t>
+  </si>
+  <si>
+    <t>7022 1670 0002 3391 4738</t>
+  </si>
+  <si>
+    <t>Sorensen Landscape Co</t>
+  </si>
+  <si>
+    <t>Granite Bay</t>
+  </si>
+  <si>
+    <t>Punch list on plant replacement, final invoice held</t>
+  </si>
+  <si>
+    <t>09/28/2026</t>
   </si>
 </sst>
 </file>
@@ -604,7 +926,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
       <sz val="9"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -678,7 +999,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -984,31 +1305,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="26" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -1033,385 +1353,395 @@
       <c r="H4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>17</v>
       </c>
       <c r="H5" s="5">
         <v>685000</v>
       </c>
-      <c r="I5" s="4" t="s">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="C6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="H6" s="5">
         <v>412000</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="E7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="H7" s="5">
+        <v>96000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="B8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="5">
+      <c r="C8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="5">
         <v>271300</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="4" t="s">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="B9" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="C9" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="H8" s="5">
+      <c r="G9" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="5">
+        <v>141500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" s="5">
         <v>512400</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B9" s="4" t="s">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="5">
+        <v>142650</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="5">
+        <v>298750</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="5">
+        <v>84500</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H14" s="5">
+        <v>444600</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H15" s="5">
+        <v>194300</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" s="5">
+        <v>58600</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" s="5">
+        <v>186900</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="H18" s="5">
+        <v>76900</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H9" s="5">
-        <v>142650</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H10" s="5">
-        <v>298750</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H11" s="5">
-        <v>444600</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H12" s="5">
-        <v>194300</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="H13" s="5">
-        <v>186900</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H14" s="5">
-        <v>76900</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H15" s="5">
+      <c r="D19" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" s="5">
         <v>68500</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" s="5">
-        <v>88400</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="H17" s="5">
-        <v>61250</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -1442,375 +1772,375 @@
     <col min="17" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="B5" s="4">
         <v>6</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>104</v>
+      <c r="C5" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E5" s="5">
         <v>112765</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K5" s="4">
         <v>3</v>
       </c>
-      <c r="L5" s="4" t="s">
-        <v>104</v>
+      <c r="L5" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N5" s="5">
         <v>152950</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P5" s="4"/>
       <c r="Q5" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="B6" s="4">
         <v>7</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>104</v>
+      <c r="C6" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E6" s="5">
         <v>64790</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K6" s="4">
         <v>4</v>
       </c>
-      <c r="L6" s="4" t="s">
-        <v>104</v>
+      <c r="L6" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N6" s="5">
         <v>121600</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P6" s="4"/>
       <c r="Q6" s="4" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="B7" s="4">
         <v>6</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>104</v>
+      <c r="C7" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E7" s="5">
         <v>12825</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K7" s="4">
         <v>5</v>
       </c>
-      <c r="L7" s="4" t="s">
-        <v>104</v>
+      <c r="L7" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N7" s="5">
         <v>98325</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P7" s="4"/>
       <c r="Q7" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="B8" s="4">
         <v>7</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>104</v>
+      <c r="C8" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E8" s="5">
         <v>21755</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K8" s="4">
         <v>6</v>
       </c>
-      <c r="L8" s="4" t="s">
-        <v>104</v>
+      <c r="L8" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N8" s="5">
         <v>89305</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P8" s="4"/>
       <c r="Q8" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="B9" s="4">
         <v>8</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>104</v>
+      <c r="C9" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E9" s="5">
         <v>38475</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>121</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K9" s="4">
         <v>7</v>
       </c>
-      <c r="L9" s="4" t="s">
-        <v>104</v>
+      <c r="L9" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="5">
         <v>120113</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P9" s="4"/>
       <c r="Q9" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="B10" s="4">
-        <v>5</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>104</v>
+        <v>6</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="E10" s="5">
-        <v>8700</v>
+        <v>31350</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K10" s="4">
         <v>8</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="6" t="s">
         <v>122</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N10" s="5">
         <v>41230</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P10" s="4" t="s">
         <v>123</v>
@@ -1824,734 +2154,707 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4">
-        <v>6</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>104</v>
+        <v>5</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="E11" s="5">
-        <v>46170</v>
+        <v>8700</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K11" s="4"/>
+      <c r="L11" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="N11" s="5">
+        <v>27227</v>
+      </c>
+      <c r="O11" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" s="4">
-        <v>3</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="N11" s="5">
-        <v>61370</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="P11" s="4"/>
+      <c r="P11" s="4" t="s">
+        <v>126</v>
+      </c>
       <c r="Q11" s="4" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B12" s="4">
-        <v>7</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>104</v>
+        <v>6</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E12" s="5">
-        <v>100515</v>
+        <v>46170</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K12" s="4">
-        <v>4</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>104</v>
+        <v>3</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="M12" s="4" t="s">
         <v>110</v>
       </c>
       <c r="N12" s="5">
-        <v>48830</v>
+        <v>61370</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P12" s="4"/>
       <c r="Q12" s="4" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="B13" s="4">
         <v>7</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>104</v>
+      <c r="C13" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E13" s="5">
-        <v>29750</v>
+        <v>100515</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K13" s="4">
-        <v>7</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>104</v>
+        <v>4</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N13" s="5">
-        <v>116525</v>
+        <v>48830</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P13" s="4"/>
       <c r="Q13" s="4" t="s">
-        <v>125</v>
+        <v>71</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="B14" s="4">
         <v>8</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>104</v>
+      <c r="C14" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E14" s="5">
-        <v>28437.5</v>
+        <v>29200</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K14" s="4">
-        <v>8</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>104</v>
+        <v>7</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="N14" s="5">
-        <v>37166</v>
+        <v>116525</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P14" s="4"/>
       <c r="Q14" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B15" s="4">
         <v>4</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>104</v>
+      <c r="C15" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E15" s="5">
         <v>95410</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K15" s="4">
-        <v>4</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>104</v>
+        <v>8</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="N15" s="5">
-        <v>164730</v>
+        <v>37166</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P15" s="4"/>
       <c r="Q15" s="4" t="s">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B16" s="4">
         <v>5</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>104</v>
+      <c r="C16" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E16" s="5">
         <v>173465</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K16" s="4">
-        <v>5</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>104</v>
+        <v>4</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="N16" s="5">
-        <v>194370</v>
+        <v>164730</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P16" s="4"/>
       <c r="Q16" s="4" t="s">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B17" s="4">
         <v>7</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>112</v>
-      </c>
+      <c r="C17" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D17" s="4"/>
       <c r="E17" s="5">
         <v>14937.5</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K17" s="4">
-        <v>6</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>104</v>
+        <v>5</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="N17" s="5">
-        <v>106400</v>
+        <v>194370</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P17" s="4"/>
       <c r="Q17" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B18" s="4">
         <v>4</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>104</v>
+      <c r="C18" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E18" s="5">
         <v>32110</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="K18" s="4">
-        <v>7</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>104</v>
+        <v>6</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="N18" s="5">
-        <v>21280</v>
+        <v>106400</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P18" s="4"/>
       <c r="Q18" s="4" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B19" s="4">
         <v>5</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>104</v>
+      <c r="C19" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E19" s="5">
         <v>97565</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>73</v>
+        <v>37</v>
       </c>
       <c r="K19" s="4">
         <v>7</v>
       </c>
-      <c r="L19" s="4" t="s">
-        <v>104</v>
+      <c r="L19" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N19" s="5">
-        <v>44200</v>
+        <v>21280</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P19" s="4"/>
       <c r="Q19" s="4" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B20" s="4">
         <v>6</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>104</v>
+      <c r="C20" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E20" s="5">
         <v>66860</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="K20" s="4">
-        <v>8</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>131</v>
+        <v>3</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="N20" s="5">
-        <v>4420</v>
+        <v>71250</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P20" s="4"/>
       <c r="Q20" s="4" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B21" s="4">
         <v>7</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>104</v>
+      <c r="C21" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E21" s="5">
         <v>88920</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K21" s="4">
-        <v>3</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>104</v>
+        <v>4</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N21" s="5">
-        <v>71250</v>
+        <v>158650</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P21" s="4"/>
       <c r="Q21" s="4" t="s">
-        <v>134</v>
+        <v>71</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B22" s="4">
         <v>8</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="6" t="s">
         <v>122</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E22" s="5">
         <v>73910</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>121</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K22" s="4">
-        <v>4</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>104</v>
+        <v>5</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="N22" s="5">
-        <v>158650</v>
+        <v>143710</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P22" s="4"/>
       <c r="Q22" s="4" t="s">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B23" s="4">
         <v>5</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>104</v>
+      <c r="C23" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E23" s="5">
         <v>69501.5</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K23" s="4">
-        <v>5</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>104</v>
+        <v>6</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="N23" s="5">
-        <v>143710</v>
+        <v>12675</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="P23" s="4"/>
       <c r="Q23" s="4" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="30" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B24" s="4">
         <v>7</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>104</v>
+      <c r="C24" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E24" s="5">
         <v>66016</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K24" s="4">
-        <v>6</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="M24" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="N24" s="5">
-        <v>12675</v>
-      </c>
-      <c r="O24" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="R24" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2561,55 +2864,54 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="40" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="44" customWidth="1"/>
+    <col min="9" max="10" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -2617,10 +2919,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="D4" s="5">
         <v>128640</v>
@@ -2635,13 +2937,13 @@
         <v>10877</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -2649,10 +2951,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D5" s="5">
         <v>333670</v>
@@ -2667,13 +2969,13 @@
         <v>10880</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -2681,10 +2983,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D6" s="5">
         <v>719435</v>
@@ -2699,13 +3001,13 @@
         <v>10885</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -2713,10 +3015,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D7" s="5">
         <v>901415</v>
@@ -2731,13 +3033,13 @@
         <v>10889</v>
       </c>
       <c r="H7" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -2745,10 +3047,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D8" s="5">
         <v>643750</v>
@@ -2763,13 +3065,13 @@
         <v>10895</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>81</v>
+        <v>160</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>83</v>
+        <v>161</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -2777,10 +3079,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D9" s="5">
         <v>656610</v>
@@ -2795,13 +3097,13 @@
         <v>10898</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -2809,31 +3111,31 @@
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D10" s="5">
-        <v>254775</v>
+        <v>312390</v>
       </c>
       <c r="E10" s="5">
-        <v>12738.75</v>
+        <v>15619.5</v>
       </c>
       <c r="F10" s="5">
-        <v>242036.25</v>
+        <v>296770.5</v>
       </c>
       <c r="G10" s="4">
         <v>10905</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -2841,16 +3143,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>121</v>
       </c>
       <c r="D11" s="5">
-        <v>109955</v>
+        <v>98340</v>
       </c>
       <c r="E11" s="5">
-        <v>5497.75</v>
+        <v>4917</v>
       </c>
       <c r="F11" s="5">
         <v>0</v>
@@ -2859,12 +3161,12 @@
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -2877,29 +3179,150 @@
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D13" s="8">
         <f>SUM(D4:D12)</f>
-        <v>3748250</v>
+        <v>3794250</v>
       </c>
       <c r="E13" s="8">
         <f>SUM(E4:E12)</f>
-        <v>187412.5</v>
+        <v>189712.5</v>
       </c>
       <c r="F13" s="8">
         <f>SUM(F4:F12)</f>
-        <v>3456380.25</v>
+        <v>3511114.5</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D18" s="5">
+        <v>14900</v>
+      </c>
+      <c r="E18" s="5">
+        <v>14900</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19" s="5">
+        <v>27350</v>
+      </c>
+      <c r="E19" s="5">
+        <v>27350</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="G19" s="5">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D20" s="5">
+        <v>88400</v>
+      </c>
+      <c r="E20" s="5">
+        <v>63320</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>164</v>
+      </c>
+      <c r="G20" s="5">
+        <v>25080</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -2909,54 +3332,54 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="44" customWidth="1"/>
+    <col min="7" max="7" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>170</v>
+        <v>199</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>171</v>
+        <v>200</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>172</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="C4" s="4" t="s">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="D4" s="5">
         <v>685000</v>
@@ -2968,18 +3391,18 @@
         <v>0.05</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>174</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="D5" s="5">
         <v>412000</v>
@@ -2991,18 +3414,18 @@
         <v>0.05</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>176</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="D6" s="5">
         <v>271300</v>
@@ -3014,18 +3437,18 @@
         <v>0.05</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>178</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D7" s="5">
         <v>512400</v>
@@ -3037,18 +3460,18 @@
         <v>0.05</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>179</v>
+        <v>35</v>
       </c>
       <c r="D8" s="5">
         <v>142650</v>
@@ -3063,13 +3486,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D9" s="5">
         <v>444600</v>
@@ -3081,18 +3504,18 @@
         <v>0.05</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>180</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>181</v>
+        <v>207</v>
       </c>
       <c r="D10" s="5">
         <v>298750</v>
@@ -3107,13 +3530,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="D11" s="5">
         <v>194300</v>
@@ -3128,13 +3551,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="D12" s="5">
         <v>186900</v>
@@ -3149,19 +3572,19 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>116</v>
+        <v>209</v>
       </c>
       <c r="D13" s="5">
-        <v>76900</v>
+        <v>58600</v>
       </c>
       <c r="E13" s="5">
-        <v>4280</v>
+        <v>0</v>
       </c>
       <c r="F13" s="9">
         <v>0.05</v>
@@ -3170,45 +3593,490 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>183</v>
+        <v>117</v>
       </c>
       <c r="D14" s="5">
-        <v>88400</v>
+        <v>76900</v>
       </c>
       <c r="E14" s="5">
-        <v>0</v>
+        <v>4280</v>
       </c>
       <c r="F14" s="9">
         <v>0.05</v>
       </c>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="56" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>79</v>
+        <v>239</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" s="5">
-        <v>61250</v>
-      </c>
-      <c r="E15" s="5">
-        <v>0</v>
-      </c>
-      <c r="F15" s="9">
-        <v>0.05</v>
-      </c>
-      <c r="G15" s="4"/>
+        <v>258</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>290</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/submissions/11-lien-analysis-larkspur/inputs/owner_project_file_larkspur.xlsx
+++ b/submissions/11-lien-analysis-larkspur/inputs/owner_project_file_larkspur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8C10F3-AC3A-E44D-8FCF-FD61E39C389F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD290AD-55DB-514F-8493-5C6BB125D88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="21600" windowHeight="36520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="302">
   <si>
     <t>Preliminary notices received, Larkspur Crossing Building B, job file 2210-B</t>
   </si>
@@ -466,7 +466,19 @@
     <t>Letter says all claims for the May billing and retention are released on payment of the balance</t>
   </si>
   <si>
-    <t>Payments by the owner, Larkspur Crossing Building B. Dunmore-Kettle Builders, Inc., contract sum $3,748,250.00, approved change orders 1 to 6 $46,000.00, adjusted contract sum $3,794,250.00, retention 5 percent</t>
+    <t>Disputed claims for extras: $14,540.00</t>
+  </si>
+  <si>
+    <t>Dunmore-Kettle Builders check 4488</t>
+  </si>
+  <si>
+    <t>10/08/2026</t>
+  </si>
+  <si>
+    <t>10/12/2026</t>
+  </si>
+  <si>
+    <t>Payments by the owner, Larkspur Crossing Building B. Dunmore-Kettle Builders, Inc., contract sum $3,748,250.00, approved change orders 1 to 6 $80,000.00, adjusted contract sum $3,828,250.00, retention 5 percent</t>
   </si>
   <si>
     <t>PERIOD_THROUGH</t>
@@ -652,7 +664,7 @@
     <t>01/22/2026</t>
   </si>
   <si>
-    <t>Norman S. Wright; Sierra Test and Balance (sub-tier)</t>
+    <t>Pacific Comfort Products; Granite Bay Sheet Metal; Sierra Test and Balance (sub-tier)</t>
   </si>
   <si>
     <t>02/26/2026</t>
@@ -859,6 +871,12 @@
     <t>09/11/2026</t>
   </si>
   <si>
+    <t>7022 1670 0002 3391 4382</t>
+  </si>
+  <si>
+    <t>Sierra Test and Balance</t>
+  </si>
+  <si>
     <t>7022 1670 0002 3391 4399</t>
   </si>
   <si>
@@ -905,6 +923,21 @@
   </si>
   <si>
     <t>09/28/2026</t>
+  </si>
+  <si>
+    <t>Returned mail, job file 2210-B</t>
+  </si>
+  <si>
+    <t>DATE_RETURNED</t>
+  </si>
+  <si>
+    <t>REASON</t>
+  </si>
+  <si>
+    <t>09/29/2026</t>
+  </si>
+  <si>
+    <t>Unclaimed, returned to sender</t>
   </si>
 </sst>
 </file>
@@ -2856,6 +2889,30 @@
       <c r="I24" s="4" t="s">
         <v>114</v>
       </c>
+      <c r="J24" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24">
+        <v>8</v>
+      </c>
+      <c r="L24" t="s">
+        <v>134</v>
+      </c>
+      <c r="N24">
+        <v>8940</v>
+      </c>
+      <c r="O24" t="s">
+        <v>144</v>
+      </c>
+      <c r="P24" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>146</v>
+      </c>
+      <c r="R24" t="s">
+        <v>147</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2879,7 +2936,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -2887,31 +2944,31 @@
         <v>89</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -2919,7 +2976,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>36</v>
@@ -2937,13 +2994,13 @@
         <v>10877</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -2972,10 +3029,10 @@
         <v>59</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -3001,13 +3058,13 @@
         <v>10885</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>64</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -3033,13 +3090,13 @@
         <v>10889</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>79</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -3065,13 +3122,13 @@
         <v>10895</v>
       </c>
       <c r="H8" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="J8" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -3097,13 +3154,13 @@
         <v>10898</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -3129,13 +3186,13 @@
         <v>10905</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>140</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -3149,10 +3206,10 @@
         <v>121</v>
       </c>
       <c r="D11" s="5">
-        <v>98340</v>
+        <v>132340</v>
       </c>
       <c r="E11" s="5">
-        <v>4917</v>
+        <v>6617</v>
       </c>
       <c r="F11" s="5">
         <v>0</v>
@@ -3161,12 +3218,12 @@
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -3179,20 +3236,20 @@
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="D13" s="8">
         <f>SUM(D4:D12)</f>
-        <v>3794250</v>
+        <v>3828250</v>
       </c>
       <c r="E13" s="8">
         <f>SUM(E4:E12)</f>
-        <v>189712.5</v>
+        <v>191412.5</v>
       </c>
       <c r="F13" s="8">
         <f>SUM(F4:F12)</f>
@@ -3201,52 +3258,52 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D18" s="5">
         <v>14900</v>
@@ -3255,27 +3312,27 @@
         <v>14900</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G18" s="5">
         <v>0</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D19" s="5">
         <v>27350</v>
@@ -3284,27 +3341,27 @@
         <v>27350</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G19" s="5">
         <v>0</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D20" s="5">
         <v>88400</v>
@@ -3313,16 +3370,16 @@
         <v>63320</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G20" s="5">
         <v>25080</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -3345,30 +3402,30 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -3379,7 +3436,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D4" s="5">
         <v>685000</v>
@@ -3402,7 +3459,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D5" s="5">
         <v>412000</v>
@@ -3414,7 +3471,7 @@
         <v>0.05</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -3425,7 +3482,7 @@
         <v>29</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D6" s="5">
         <v>271300</v>
@@ -3492,7 +3549,7 @@
         <v>58</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D9" s="5">
         <v>444600</v>
@@ -3504,7 +3561,7 @@
         <v>0.05</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -3515,7 +3572,7 @@
         <v>49</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D10" s="5">
         <v>298750</v>
@@ -3557,7 +3614,7 @@
         <v>73</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D12" s="5">
         <v>186900</v>
@@ -3578,7 +3635,7 @@
         <v>68</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D13" s="5">
         <v>58600</v>
@@ -3619,7 +3676,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -3632,12 +3689,12 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -3645,59 +3702,59 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -3705,16 +3762,16 @@
         <v>113</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>116</v>
@@ -3722,360 +3779,407 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>248</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>43</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>235</v>
-      </c>
       <c r="D17" s="4" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="F21" s="4"/>
+        <v>247</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>225</v>
+        <v>282</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>226</v>
+        <v>255</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>270</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>279</v>
+        <v>229</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>225</v>
+        <v>285</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>283</v>
+        <v>247</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>287</v>
+        <v>229</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>288</v>
+        <v>230</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>289</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>290</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>

--- a/submissions/11-lien-analysis-larkspur/inputs/owner_project_file_larkspur.xlsx
+++ b/submissions/11-lien-analysis-larkspur/inputs/owner_project_file_larkspur.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD290AD-55DB-514F-8493-5C6BB125D88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF4C1414-4665-FC40-95EB-15A5AEFC9528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="21600" windowHeight="36520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="651" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="308">
   <si>
     <t>Preliminary notices received, Larkspur Crossing Building B, job file 2210-B</t>
   </si>
@@ -163,6 +163,21 @@
     <t>02/23/2026</t>
   </si>
   <si>
+    <t>Auburn Scaffold &amp; Shoring, Inc.</t>
+  </si>
+  <si>
+    <t>Scaffold and shoring rental</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
+    <t>03/05/2026</t>
+  </si>
+  <si>
+    <t>03/09/2026</t>
+  </si>
+  <si>
     <t>Lindqvist Fire Protection</t>
   </si>
   <si>
@@ -172,9 +187,6 @@
     <t>03/06/2026</t>
   </si>
   <si>
-    <t>03/09/2026</t>
-  </si>
-  <si>
     <t>03/11/2026</t>
   </si>
   <si>
@@ -202,9 +214,6 @@
     <t>03/18/2026</t>
   </si>
   <si>
-    <t>03/03/2026</t>
-  </si>
-  <si>
     <t>Kastner Mechanical Contractors, Inc.</t>
   </si>
   <si>
@@ -478,7 +487,7 @@
     <t>10/12/2026</t>
   </si>
   <si>
-    <t>Payments by the owner, Larkspur Crossing Building B. Dunmore-Kettle Builders, Inc., contract sum $3,748,250.00, approved change orders 1 to 6 $80,000.00, adjusted contract sum $3,828,250.00, retention 5 percent</t>
+    <t>Payments by the owner, Larkspur Crossing Building B. Dunmore-Kettle Builders, Inc., contract sum $3,748,250.00, approved change orders 1 to 6 $100,000.00, adjusted contract sum $3,848,250.00, retention 5 percent</t>
   </si>
   <si>
     <t>PERIOD_THROUGH</t>
@@ -664,6 +673,9 @@
     <t>01/22/2026</t>
   </si>
   <si>
+    <t>Hedrick &amp; Sons Building Supply; Auburn Scaffold &amp; Shoring</t>
+  </si>
+  <si>
     <t>Pacific Comfort Products; Granite Bay Sheet Metal; Sierra Test and Balance (sub-tier)</t>
   </si>
   <si>
@@ -838,6 +850,15 @@
     <t>7022 1670 0002 3391 4283</t>
   </si>
   <si>
+    <t>7022 1670 0002 3391 4290</t>
+  </si>
+  <si>
+    <t>Auburn Scaffold and Shoring</t>
+  </si>
+  <si>
+    <t>Auburn</t>
+  </si>
+  <si>
     <t>09/08/2026</t>
   </si>
   <si>
@@ -863,9 +884,6 @@
   </si>
   <si>
     <t>Hedrick and Sons Bldg Supply</t>
-  </si>
-  <si>
-    <t>Auburn</t>
   </si>
   <si>
     <t>09/11/2026</t>
@@ -1338,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -1551,7 +1569,7 @@
         <v>44</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>45</v>
@@ -1563,10 +1581,10 @@
         <v>47</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H11" s="5">
-        <v>142650</v>
+        <v>36000</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -1580,19 +1598,19 @@
         <v>12</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>51</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H12" s="5">
-        <v>298750</v>
+        <v>142650</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
@@ -1603,177 +1621,203 @@
         <v>53</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="H13" s="5">
-        <v>84500</v>
+        <v>298750</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="C14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="G14" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H14" s="5">
-        <v>444600</v>
+        <v>84500</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>62</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>65</v>
-      </c>
       <c r="G15" s="4" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="H15" s="5">
-        <v>194300</v>
+        <v>444600</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>63</v>
-      </c>
       <c r="H16" s="5">
-        <v>58600</v>
+        <v>194300</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E17" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>75</v>
-      </c>
       <c r="G17" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H17" s="5">
-        <v>186900</v>
+        <v>58600</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="G18" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H18" s="5">
-        <v>76900</v>
+        <v>186900</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="G19" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H19" s="5">
+        <v>76900</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="H19" s="5">
+      <c r="D20" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H20" s="5">
         <v>68500</v>
       </c>
     </row>
@@ -1807,95 +1851,95 @@
   <sheetData>
     <row r="1" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B5" s="4">
         <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E5" s="5">
         <v>112765</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>10</v>
@@ -1904,50 +1948,50 @@
         <v>3</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N5" s="5">
         <v>152950</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P5" s="4"/>
       <c r="Q5" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B6" s="4">
         <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E6" s="5">
         <v>64790</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>10</v>
@@ -1956,50 +2000,50 @@
         <v>4</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="N6" s="5">
         <v>121600</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P6" s="4"/>
       <c r="Q6" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B7" s="4">
         <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E7" s="5">
         <v>12825</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>10</v>
@@ -2008,50 +2052,50 @@
         <v>5</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N7" s="5">
         <v>98325</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P7" s="4"/>
       <c r="Q7" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="R7" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B8" s="4">
         <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E8" s="5">
         <v>21755</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>10</v>
@@ -2060,50 +2104,50 @@
         <v>6</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="N8" s="5">
         <v>89305</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P8" s="4"/>
       <c r="Q8" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="R8" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B9" s="4">
         <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E9" s="5">
         <v>38475</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>10</v>
@@ -2112,50 +2156,50 @@
         <v>7</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N9" s="5">
         <v>120113</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P9" s="4"/>
       <c r="Q9" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="R9" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B10" s="4">
         <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E10" s="5">
         <v>31350</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>10</v>
@@ -2164,104 +2208,104 @@
         <v>8</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="N10" s="5">
         <v>41230</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="Q10" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="R10" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="R10" s="4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B11" s="4">
         <v>5</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E11" s="5">
         <v>8700</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>10</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N11" s="5">
         <v>27227</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Q11" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B12" s="4">
         <v>6</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E12" s="5">
         <v>46170</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>28</v>
@@ -2270,50 +2314,50 @@
         <v>3</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N12" s="5">
         <v>61370</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P12" s="4"/>
       <c r="Q12" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B13" s="4">
         <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E13" s="5">
         <v>100515</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>28</v>
@@ -2322,50 +2366,50 @@
         <v>4</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="N13" s="5">
         <v>48830</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P13" s="4"/>
       <c r="Q13" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B14" s="4">
         <v>8</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E14" s="5">
         <v>29200</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>28</v>
@@ -2374,50 +2418,50 @@
         <v>7</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N14" s="5">
         <v>116525</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P14" s="4"/>
       <c r="Q14" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B15" s="4">
         <v>4</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E15" s="5">
         <v>95410</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>28</v>
@@ -2426,50 +2470,50 @@
         <v>8</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="N15" s="5">
         <v>37166</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P15" s="4"/>
       <c r="Q15" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B16" s="4">
         <v>5</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E16" s="5">
         <v>173465</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>37</v>
@@ -2478,50 +2522,50 @@
         <v>4</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="N16" s="5">
         <v>164730</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P16" s="4"/>
       <c r="Q16" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B17" s="4">
         <v>7</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="5">
         <v>14937.5</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>37</v>
@@ -2530,50 +2574,50 @@
         <v>5</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N17" s="5">
         <v>194370</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P17" s="4"/>
       <c r="Q17" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B18" s="4">
         <v>4</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E18" s="5">
         <v>32110</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>37</v>
@@ -2582,50 +2626,50 @@
         <v>6</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="N18" s="5">
         <v>106400</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P18" s="4"/>
       <c r="Q18" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="R18" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B19" s="4">
         <v>5</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E19" s="5">
         <v>97565</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>37</v>
@@ -2634,50 +2678,50 @@
         <v>7</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="N19" s="5">
         <v>21280</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P19" s="4"/>
       <c r="Q19" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="R19" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B20" s="4">
         <v>6</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E20" s="5">
         <v>66860</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>17</v>
@@ -2686,50 +2730,50 @@
         <v>3</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N20" s="5">
         <v>71250</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P20" s="4"/>
       <c r="Q20" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="R20" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B21" s="4">
         <v>7</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E21" s="5">
         <v>88920</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>17</v>
@@ -2738,52 +2782,52 @@
         <v>4</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="N21" s="5">
         <v>158650</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P21" s="4"/>
       <c r="Q21" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="R21" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B22" s="4">
         <v>8</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E22" s="5">
         <v>73910</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>17</v>
@@ -2792,50 +2836,50 @@
         <v>5</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N22" s="5">
         <v>143710</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="P22" s="4"/>
       <c r="Q22" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B23" s="4">
         <v>5</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E23" s="5">
         <v>69501.5</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>17</v>
@@ -2844,50 +2888,50 @@
         <v>6</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="N23" s="5">
         <v>12675</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="P23" s="4"/>
       <c r="Q23" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B24" s="4">
         <v>7</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E24" s="5">
         <v>66016</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J24" t="s">
         <v>32</v>
@@ -2896,22 +2940,22 @@
         <v>8</v>
       </c>
       <c r="L24" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="N24">
         <v>8940</v>
       </c>
       <c r="O24" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="P24" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q24" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="R24" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2936,39 +2980,39 @@
   <sheetData>
     <row r="1" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -2976,7 +3020,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>36</v>
@@ -2994,13 +3038,13 @@
         <v>10877</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -3008,31 +3052,31 @@
         <v>2</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="5">
-        <v>333670</v>
+        <v>333680</v>
       </c>
       <c r="E5" s="5">
-        <v>16683.5</v>
+        <v>16684</v>
       </c>
       <c r="F5" s="5">
-        <v>316986.5</v>
+        <v>316996</v>
       </c>
       <c r="G5" s="4">
         <v>10880</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -3040,10 +3084,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D6" s="5">
         <v>719435</v>
@@ -3058,13 +3102,13 @@
         <v>10885</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -3072,10 +3116,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D7" s="5">
         <v>901415</v>
@@ -3090,13 +3134,13 @@
         <v>10889</v>
       </c>
       <c r="H7" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -3104,10 +3148,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D8" s="5">
         <v>643750</v>
@@ -3122,13 +3166,13 @@
         <v>10895</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -3136,10 +3180,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D9" s="5">
         <v>656610</v>
@@ -3154,13 +3198,13 @@
         <v>10898</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -3168,10 +3212,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D10" s="5">
         <v>312390</v>
@@ -3186,13 +3230,13 @@
         <v>10905</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -3200,16 +3244,16 @@
         <v>8</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D11" s="5">
-        <v>132340</v>
+        <v>152330</v>
       </c>
       <c r="E11" s="5">
-        <v>6617</v>
+        <v>7616.5</v>
       </c>
       <c r="F11" s="5">
         <v>0</v>
@@ -3218,12 +3262,12 @@
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -3236,74 +3280,74 @@
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D13" s="8">
         <f>SUM(D4:D12)</f>
-        <v>3828250</v>
+        <v>3848250</v>
       </c>
       <c r="E13" s="8">
         <f>SUM(E4:E12)</f>
-        <v>191412.5</v>
+        <v>192412.5</v>
       </c>
       <c r="F13" s="8">
         <f>SUM(F4:F12)</f>
-        <v>3511114.5</v>
+        <v>3511124</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D18" s="5">
         <v>14900</v>
@@ -3312,27 +3356,27 @@
         <v>14900</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G18" s="5">
         <v>0</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D19" s="5">
         <v>27350</v>
@@ -3341,27 +3385,27 @@
         <v>27350</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G19" s="5">
         <v>0</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D20" s="5">
         <v>88400</v>
@@ -3370,16 +3414,16 @@
         <v>63320</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G20" s="5">
         <v>25080</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -3402,30 +3446,30 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -3436,7 +3480,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D4" s="5">
         <v>685000</v>
@@ -3459,7 +3503,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D5" s="5">
         <v>412000</v>
@@ -3471,7 +3515,7 @@
         <v>0.05</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -3482,7 +3526,7 @@
         <v>29</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D6" s="5">
         <v>271300</v>
@@ -3494,7 +3538,7 @@
         <v>0.05</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -3517,15 +3561,15 @@
         <v>0.05</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>82</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>35</v>
@@ -3543,13 +3587,13 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D9" s="5">
         <v>444600</v>
@@ -3561,18 +3605,18 @@
         <v>0.05</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D10" s="5">
         <v>298750</v>
@@ -3587,13 +3631,13 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D11" s="5">
         <v>194300</v>
@@ -3608,13 +3652,13 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="D12" s="5">
         <v>186900</v>
@@ -3629,13 +3673,13 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="D13" s="5">
         <v>58600</v>
@@ -3650,13 +3694,13 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D14" s="5">
         <v>76900</v>
@@ -3676,7 +3720,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -3689,12 +3733,12 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -3702,451 +3746,451 @@
         <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>252</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>254</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>239</v>
-      </c>
       <c r="D17" s="4" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>224</v>
+        <v>274</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>277</v>
+        <v>228</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="F22" s="4"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>229</v>
+        <v>288</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>230</v>
+        <v>259</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>274</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="F23" s="4"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>285</v>
+        <v>233</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>229</v>
+        <v>291</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>289</v>
+        <v>251</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>293</v>
+        <v>233</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>294</v>
+        <v>234</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>295</v>
@@ -4155,31 +4199,52 @@
         <v>296</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
+      <c r="B27" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="C27" s="4" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
+      <c r="D27" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="C30" s="4" t="s">
+      <c r="E27" s="4" t="s">
         <v>301</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="30" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>307</v>
       </c>
     </row>
   </sheetData>
